--- a/DeskTop_Version/data/Test_Import_Template.xlsx
+++ b/DeskTop_Version/data/Test_Import_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\attensync\salarySync\DeskTop_Version\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3C3A6E-2F12-43A9-A4F9-27959BCF2691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABFD8FB-05D9-465E-8AB2-A85A82C2FE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="companies" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
   <si>
     <t>code</t>
   </si>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t>Mehedi</t>
-  </si>
-  <si>
-    <t>Sayem</t>
   </si>
   <si>
     <t>Friday</t>
@@ -206,7 +203,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,26 +216,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7B7B7"/>
-        <bgColor rgb="FFB7B7B7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -270,26 +249,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -297,30 +261,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="18" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -692,11 +632,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>46037</v>
+      <c r="A2" s="3">
+        <v>46058</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
@@ -705,7 +645,7 @@
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2">
         <v>1000</v>
@@ -722,10 +662,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.44140625" customWidth="1"/>
@@ -757,58 +697,18 @@
         <v>500001</v>
       </c>
       <c r="B2" s="2">
-        <v>46025</v>
-      </c>
-      <c r="C2" s="13">
+        <v>46057</v>
+      </c>
+      <c r="C2" s="5">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="5">
         <v>0.5</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>500002</v>
-      </c>
-      <c r="B3" s="2">
-        <v>46026</v>
-      </c>
-      <c r="C3" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D3" s="13">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>500001</v>
-      </c>
-      <c r="B4" s="2">
-        <v>46027</v>
-      </c>
-      <c r="C4" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D4" s="13">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -995,7 +895,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -1083,36 +983,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>500002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="2">
-        <v>44694</v>
-      </c>
-      <c r="D3">
-        <v>20000</v>
-      </c>
-      <c r="E3">
-        <v>1000</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C4" s="2"/>
@@ -1149,9 +1020,6 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C16" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1162,7 +1030,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -1192,10 +1060,10 @@
         <v>46023</v>
       </c>
       <c r="C2" s="4">
-        <v>0.43125000000000002</v>
+        <v>0.33680555555555558</v>
       </c>
       <c r="D2" s="4">
-        <v>0.86458333333333337</v>
+        <v>0.70833333333333337</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1203,789 +1071,13 @@
         <v>500001</v>
       </c>
       <c r="B3" s="3">
-        <v>46024</v>
+        <v>46057</v>
       </c>
       <c r="C3" s="4">
-        <v>0.42986111111111114</v>
+        <v>0.34375</v>
       </c>
       <c r="D3" s="4">
-        <v>0.85486111111111107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>500001</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46025</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0.42986111111111114</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>500001</v>
-      </c>
-      <c r="B5" s="3">
-        <v>46026</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.43125000000000002</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.89236111111111116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>500001</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46027</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>500001</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46028</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0.42986111111111114</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0.86944444444444446</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>500001</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46029</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0.42916666666666664</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.86944444444444446</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>500001</v>
-      </c>
-      <c r="B9" s="3">
-        <v>46030</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.43194444444444446</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.87222222222222223</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>500001</v>
-      </c>
-      <c r="B10" s="3">
-        <v>46031</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0.43194444444444446</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.86041666666666672</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>500001</v>
-      </c>
-      <c r="B11" s="3">
-        <v>46032</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.86805555555555558</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>500001</v>
-      </c>
-      <c r="B12" s="3">
-        <v>46033</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0.4375</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.86458333333333337</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>500001</v>
-      </c>
-      <c r="B13" s="3">
-        <v>46034</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>500001</v>
-      </c>
-      <c r="B14" s="3">
-        <v>46035</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0.43472222222222223</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.86527777777777781</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>500001</v>
-      </c>
-      <c r="B15" s="3">
-        <v>46036</v>
-      </c>
-      <c r="C15" s="9">
-        <v>0.43194444444444446</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.86319444444444449</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>500001</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46037</v>
-      </c>
-      <c r="C16" s="8">
-        <v>0.42986111111111114</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0.87361111111111112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>500001</v>
-      </c>
-      <c r="B17" s="3">
-        <v>46038</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0.43263888888888891</v>
-      </c>
-      <c r="D17" s="8">
-        <v>0.86458333333333337</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>500001</v>
-      </c>
-      <c r="B18" s="3">
-        <v>46039</v>
-      </c>
-      <c r="C18" s="8">
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="D18" s="8">
-        <v>0.86944444444444446</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>500001</v>
-      </c>
-      <c r="B19" s="3">
-        <v>46040</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="D19" s="8">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>500001</v>
-      </c>
-      <c r="B20" s="3">
-        <v>46041</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>500001</v>
-      </c>
-      <c r="B21" s="3">
-        <v>46042</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0.43263888888888891</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>500001</v>
-      </c>
-      <c r="B22" s="3">
-        <v>46043</v>
-      </c>
-      <c r="C22" s="8">
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0.85486111111111107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>500001</v>
-      </c>
-      <c r="B23" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0.8666666666666667</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>500001</v>
-      </c>
-      <c r="B24" s="3">
-        <v>46045</v>
-      </c>
-      <c r="C24" s="8">
-        <v>0.43263888888888891</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0.85902777777777772</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>500001</v>
-      </c>
-      <c r="B25" s="3">
-        <v>46046</v>
-      </c>
-      <c r="C25" s="8">
-        <v>0.42986111111111114</v>
-      </c>
-      <c r="D25" s="8">
-        <v>0.86319444444444449</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>500001</v>
-      </c>
-      <c r="B26" s="3">
-        <v>46047</v>
-      </c>
-      <c r="C26" s="8">
-        <v>0.4375</v>
-      </c>
-      <c r="D26" s="8">
-        <v>0.85486111111111107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>500001</v>
-      </c>
-      <c r="B27" s="3">
-        <v>46048</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>500001</v>
-      </c>
-      <c r="B28" s="3">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0.43125000000000002</v>
-      </c>
-      <c r="D28" s="8">
-        <v>0.85902777777777772</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>500001</v>
-      </c>
-      <c r="B29" s="3">
-        <v>46050</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0.42986111111111114</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0.85763888888888884</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>500001</v>
-      </c>
-      <c r="B30" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C30" s="8">
-        <v>0.43125000000000002</v>
-      </c>
-      <c r="D30" s="8">
-        <v>0.87638888888888888</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>500001</v>
-      </c>
-      <c r="B31" s="3">
-        <v>46052</v>
-      </c>
-      <c r="C31" s="8">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D31" s="8">
-        <v>0.85624999999999996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>500002</v>
-      </c>
-      <c r="B32" s="3">
-        <v>46023</v>
-      </c>
-      <c r="C32" s="4">
-        <v>0.43402777777777779</v>
-      </c>
-      <c r="D32" s="4">
-        <v>0.86458333333333337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>500002</v>
-      </c>
-      <c r="B33" s="3">
-        <v>46024</v>
-      </c>
-      <c r="C33" s="4">
-        <v>0.43125000000000002</v>
-      </c>
-      <c r="D33" s="4">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>500002</v>
-      </c>
-      <c r="B34" s="3">
-        <v>46025</v>
-      </c>
-      <c r="C34" s="5">
-        <v>0.42986111111111114</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0.87013888888888891</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>500002</v>
-      </c>
-      <c r="B35" s="3">
-        <v>46026</v>
-      </c>
-      <c r="C35" s="4">
-        <v>0.43472222222222223</v>
-      </c>
-      <c r="D35" s="4">
-        <v>0.8930555555555556</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>500002</v>
-      </c>
-      <c r="B36" s="3">
-        <v>46027</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>500002</v>
-      </c>
-      <c r="B37" s="3">
-        <v>46028</v>
-      </c>
-      <c r="C37" s="11">
-        <v>0.43541666666666667</v>
-      </c>
-      <c r="D37" s="11">
-        <v>0.86944444444444446</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>500002</v>
-      </c>
-      <c r="B38" s="3">
-        <v>46029</v>
-      </c>
-      <c r="C38" s="8">
-        <v>0.44305555555555554</v>
-      </c>
-      <c r="D38" s="8">
-        <v>0.86944444444444446</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>500002</v>
-      </c>
-      <c r="B39" s="3">
-        <v>46030</v>
-      </c>
-      <c r="C39" s="8">
-        <v>0.43541666666666667</v>
-      </c>
-      <c r="D39" s="8">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>500002</v>
-      </c>
-      <c r="B40" s="3">
-        <v>46031</v>
-      </c>
-      <c r="C40" s="8">
-        <v>0.43611111111111112</v>
-      </c>
-      <c r="D40" s="8">
-        <v>0.86041666666666672</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>500002</v>
-      </c>
-      <c r="B41" s="3">
-        <v>46032</v>
-      </c>
-      <c r="C41" s="8">
-        <v>0.43194444444444446</v>
-      </c>
-      <c r="D41" s="8">
-        <v>0.85555555555555551</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>500002</v>
-      </c>
-      <c r="B42" s="3">
-        <v>46033</v>
-      </c>
-      <c r="C42" s="8">
-        <v>0.43194444444444446</v>
-      </c>
-      <c r="D42" s="8">
-        <v>0.86388888888888893</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>500002</v>
-      </c>
-      <c r="B43" s="3">
-        <v>46034</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>500002</v>
-      </c>
-      <c r="B44" s="3">
-        <v>46035</v>
-      </c>
-      <c r="C44" s="8">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D44" s="8">
-        <v>0.86527777777777781</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>500002</v>
-      </c>
-      <c r="B45" s="3">
-        <v>46036</v>
-      </c>
-      <c r="C45" s="9">
-        <v>0.44305555555555554</v>
-      </c>
-      <c r="D45" s="8">
-        <v>0.86527777777777781</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>500002</v>
-      </c>
-      <c r="B46" s="3">
-        <v>46037</v>
-      </c>
-      <c r="C46" s="8">
-        <v>0.43125000000000002</v>
-      </c>
-      <c r="D46" s="8">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>500002</v>
-      </c>
-      <c r="B47" s="3">
-        <v>46038</v>
-      </c>
-      <c r="C47" s="8">
-        <v>0.43194444444444446</v>
-      </c>
-      <c r="D47" s="8">
-        <v>0.86388888888888893</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>500002</v>
-      </c>
-      <c r="B48" s="3">
-        <v>46039</v>
-      </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>500002</v>
-      </c>
-      <c r="B49" s="3">
-        <v>46040</v>
-      </c>
-      <c r="C49" s="8">
-        <v>0.43472222222222223</v>
-      </c>
-      <c r="D49" s="8">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>500002</v>
-      </c>
-      <c r="B50" s="3">
-        <v>46041</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>500002</v>
-      </c>
-      <c r="B51" s="3">
-        <v>46042</v>
-      </c>
-      <c r="C51" s="8">
-        <v>0.43680555555555556</v>
-      </c>
-      <c r="D51" s="8">
-        <v>0.85902777777777772</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>500002</v>
-      </c>
-      <c r="B52" s="3">
-        <v>46043</v>
-      </c>
-      <c r="C52" s="8">
-        <v>0.43611111111111112</v>
-      </c>
-      <c r="D52" s="8">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>500002</v>
-      </c>
-      <c r="B53" s="3">
-        <v>46044</v>
-      </c>
-      <c r="C53" s="8">
-        <v>0.46944444444444444</v>
-      </c>
-      <c r="D53" s="8">
-        <v>0.86597222222222225</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>500002</v>
-      </c>
-      <c r="B54" s="3">
-        <v>46045</v>
-      </c>
-      <c r="C54" s="8">
-        <v>0.43680555555555556</v>
-      </c>
-      <c r="D54" s="8">
-        <v>0.85902777777777772</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>500002</v>
-      </c>
-      <c r="B55" s="3">
-        <v>46046</v>
-      </c>
-      <c r="C55" s="8">
-        <v>0.43263888888888891</v>
-      </c>
-      <c r="D55" s="8">
-        <v>0.86319444444444449</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>500002</v>
-      </c>
-      <c r="B56" s="3">
-        <v>46047</v>
-      </c>
-      <c r="C56" s="8">
-        <v>0.43333333333333335</v>
-      </c>
-      <c r="D56" s="8">
-        <v>0.86111111111111116</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>500002</v>
-      </c>
-      <c r="B57" s="3">
-        <v>46048</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>500002</v>
-      </c>
-      <c r="B58" s="3">
-        <v>46049</v>
-      </c>
-      <c r="C58" s="8">
-        <v>0.43680555555555556</v>
-      </c>
-      <c r="D58" s="8">
-        <v>0.85902777777777772</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>500002</v>
-      </c>
-      <c r="B59" s="3">
-        <v>46050</v>
-      </c>
-      <c r="C59" s="8">
-        <v>0.43611111111111112</v>
-      </c>
-      <c r="D59" s="8">
-        <v>0.87638888888888888</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>500002</v>
-      </c>
-      <c r="B60" s="3">
-        <v>46051</v>
-      </c>
-      <c r="C60" s="8">
-        <v>0.43472222222222223</v>
-      </c>
-      <c r="D60" s="8">
-        <v>0.88194444444444442</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>500002</v>
-      </c>
-      <c r="B61" s="3">
-        <v>46052</v>
-      </c>
-      <c r="C61" s="8">
-        <v>0.43680555555555556</v>
-      </c>
-      <c r="D61" s="8">
-        <v>0.85624999999999996</v>
+        <v>0.77152777777777781</v>
       </c>
     </row>
   </sheetData>
@@ -2021,7 +1113,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2">
         <v>1000</v>
@@ -2035,7 +1127,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3">
         <v>1000</v>
